--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536129_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536129_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,67 +807,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8376</v>
+        <v>1.7074</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8376</v>
+        <v>0.1718</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.5355</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8376</v>
+        <v>0.9562</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2301</v>
+        <v>0.352</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6075</v>
+        <v>0.6042</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8376</v>
+        <v>0.6777</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2301</v>
+        <v>0.0866</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6075</v>
+        <v>0.5911</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.2785</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.2653</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.0132</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1448</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.4158</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.2239</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.1919</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1404</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0797</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7074</v>
+        <v>1.4756</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1718</v>
+        <v>2.0386</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5355</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9562</v>
+        <v>1.6399</v>
       </c>
       <c r="H6" t="n">
-        <v>0.352</v>
+        <v>0.869</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6042</v>
+        <v>0.7709</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6777</v>
+        <v>1.3632</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0866</v>
+        <v>0.8776</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5911</v>
+        <v>0.4856</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2785</v>
+        <v>0.2768</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2653</v>
+        <v>-0.0086</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0132</v>
+        <v>0.2854</v>
       </c>
       <c r="P6" t="n">
-        <v>0.195</v>
+        <v>1.3649</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9499</v>
+        <v>-0.195</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1448</v>
+        <v>1.5599</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4158</v>
+        <v>1.0328</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2239</v>
+        <v>0.8704</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1919</v>
+        <v>0.1624</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1404</v>
+        <v>-2.5621</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0797</v>
+        <v>-2.5621</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4756</v>
+        <v>1.2626</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0386</v>
+        <v>0.7295</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0.5331</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6399</v>
+        <v>0.1368</v>
       </c>
       <c r="H7" t="n">
-        <v>0.869</v>
+        <v>0.0444</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7709</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3632</v>
+        <v>1.2882</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8776</v>
+        <v>0.6647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4856</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2768</v>
+        <v>-1.1514</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0086</v>
+        <v>-0.6202</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2854</v>
+        <v>-0.5312</v>
       </c>
       <c r="P7" t="n">
         <v>1.3649</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.195</v>
+        <v>-0.39</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5599</v>
+        <v>1.7549</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0328</v>
+        <v>-0.3265</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8704</v>
+        <v>-0.1687</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1624</v>
+        <v>-0.1578</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5621</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5621</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2626</v>
+        <v>1.1354</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7295</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5331</v>
+        <v>0.3547</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1368</v>
+        <v>-0.7951</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0444</v>
+        <v>-0.6543</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.1408</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2882</v>
+        <v>-0.1159</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6647</v>
+        <v>-0.2374</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.1215</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1514</v>
+        <v>-0.6792</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6202</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5312</v>
+        <v>-0.2623</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3649</v>
+        <v>-0.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.39</v>
+        <v>-2.5348</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7549</v>
+        <v>2.1448</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3265</v>
+        <v>1.432</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1687</v>
+        <v>0.7657</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1578</v>
+        <v>0.6663</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.6658</v>
       </c>
       <c r="X8" t="n">
-        <v>0.08749999999999999</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1354</v>
+        <v>-0.744</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7806999999999999</v>
+        <v>-0.9639</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3547</v>
+        <v>0.2199</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7951</v>
+        <v>0.7744</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6543</v>
+        <v>2.1322</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1408</v>
+        <v>-1.3577</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1159</v>
+        <v>1.9193</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2374</v>
+        <v>2.6163</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1215</v>
+        <v>-0.697</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6792</v>
+        <v>-1.1449</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4169</v>
+        <v>-0.4841</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2623</v>
+        <v>-0.6607</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.39</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.5348</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1448</v>
+        <v>1.5599</v>
       </c>
       <c r="S9" t="n">
-        <v>1.432</v>
+        <v>-0.09</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7657</v>
+        <v>-0.0169</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6663</v>
+        <v>-0.0731</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8885999999999999</v>
+        <v>-0.4535</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6658</v>
+        <v>-0.3315</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7772</v>
+        <v>-0.122</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.744</v>
+        <v>-1.051</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9639</v>
+        <v>-1.3664</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2199</v>
+        <v>0.3153</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7744</v>
+        <v>-0.0922</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1322</v>
+        <v>0.2836</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3577</v>
+        <v>-0.3758</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9193</v>
+        <v>-0.4365</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6163</v>
+        <v>0.082</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.697</v>
+        <v>-0.5185</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1449</v>
+        <v>0.3443</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4841</v>
+        <v>0.2016</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6607</v>
+        <v>0.1427</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9749</v>
+        <v>0.585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5348</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5599</v>
+        <v>0.585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09</v>
+        <v>-0.6897</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0169</v>
+        <v>-0.2669</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0731</v>
+        <v>-0.4228</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4535</v>
+        <v>-0.854</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3315</v>
+        <v>-0.6629</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.122</v>
+        <v>-0.1911</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>L. GARCIA MUNOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.051</v>
+        <v>-1.4746</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3664</v>
+        <v>-1.4933</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3153</v>
+        <v>0.0186</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0922</v>
+        <v>-1.9199</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2836</v>
+        <v>0.6076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3758</v>
+        <v>-2.5276</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4365</v>
+        <v>-0.8324</v>
       </c>
       <c r="K11" t="n">
-        <v>0.082</v>
+        <v>1.1607</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5185</v>
+        <v>-1.993</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3443</v>
+        <v>-1.0875</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2016</v>
+        <v>-0.553</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1427</v>
+        <v>-0.5345</v>
       </c>
       <c r="P11" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R11" t="n">
-        <v>0.585</v>
+        <v>2.1448</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6897</v>
+        <v>0.286</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2669</v>
+        <v>0.0355</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4228</v>
+        <v>0.2505</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.854</v>
+        <v>-1.0106</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6629</v>
+        <v>0.2786</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1911</v>
+        <v>-1.2891</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. GARCIA MUNOZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,157 +1388,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3123</v>
+        <v>20.118</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3309</v>
+        <v>16.0744</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0186</v>
+        <v>4.0433</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7575</v>
+        <v>10.2595</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6225000000000001</v>
+        <v>12.9814</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1351</v>
+        <v>-2.7221</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.67</v>
+        <v>18.3713</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0694</v>
+        <v>17.1421</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6006</v>
+        <v>1.2293</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0875</v>
+        <v>-8.111699999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.553</v>
+        <v>-4.1605</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5345</v>
+        <v>-3.9511</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1699</v>
+        <v>4.8746</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9749</v>
+        <v>-12.6741</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1448</v>
+        <v>17.5487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.286</v>
+        <v>6.482499999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0355</v>
+        <v>4.5947</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2505</v>
+        <v>1.888</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0106</v>
+        <v>-1.4985</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2786</v>
+        <v>5.782899999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2891</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>play_by_play_2536129_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-7.2814</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. RAMIREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+          <t>CB ALGECIRAS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.1179</v>
+        <v>3.7718</v>
       </c>
       <c r="E13" t="n">
-        <v>16.0744</v>
+        <v>4.0593</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0433</v>
+        <v>-0.2875</v>
       </c>
       <c r="G13" t="n">
-        <v>10.2595</v>
+        <v>1.4855</v>
       </c>
       <c r="H13" t="n">
-        <v>12.9814</v>
+        <v>-0.2141</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7221</v>
+        <v>1.6996</v>
       </c>
       <c r="J13" t="n">
-        <v>18.37130000000001</v>
+        <v>2.3732</v>
       </c>
       <c r="K13" t="n">
-        <v>17.1421</v>
+        <v>0.9556</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2292</v>
+        <v>1.4176</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.111699999999999</v>
+        <v>-0.8877</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.1605</v>
+        <v>-1.1698</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.951099999999999</v>
+        <v>0.2821</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8746</v>
+        <v>0.9749</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6741</v>
+        <v>-0.195</v>
       </c>
       <c r="R13" t="n">
-        <v>17.5487</v>
+        <v>1.1699</v>
       </c>
       <c r="S13" t="n">
-        <v>6.482499999999999</v>
+        <v>-0.7973</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5947</v>
+        <v>-0.2276</v>
       </c>
       <c r="U13" t="n">
-        <v>1.888</v>
+        <v>-0.5697</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4985</v>
+        <v>2.1086</v>
       </c>
       <c r="W13" t="n">
-        <v>5.782899999999999</v>
+        <v>2.1086</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.2814</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2536129_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. RAMIREZ SANCHEZ</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,67 +1550,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4642</v>
+        <v>2.2412</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7518</v>
+        <v>3.7543</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2875</v>
+        <v>-1.5131</v>
       </c>
       <c r="G14" t="n">
-        <v>1.178</v>
+        <v>-1.1476</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-3.6441</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6996</v>
+        <v>2.4965</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0657</v>
+        <v>1.5111</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6481</v>
+        <v>-0.9755</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4176</v>
+        <v>2.4866</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8877</v>
+        <v>-2.6588</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1698</v>
+        <v>-2.6686</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2821</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9749</v>
+        <v>1.3649</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.195</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1699</v>
+        <v>1.3649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7973</v>
+        <v>-0.9042</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2276</v>
+        <v>-0.4226</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5697</v>
+        <v>-0.4817</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1086</v>
+        <v>2.9281</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1086</v>
+        <v>2.6658</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.2624</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2412</v>
+        <v>1.1377</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7543</v>
+        <v>0.41</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5131</v>
+        <v>0.7277</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1476</v>
+        <v>0.1546</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.6441</v>
+        <v>0.1042</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4965</v>
+        <v>0.0504</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5111</v>
+        <v>0.6926</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9755</v>
+        <v>0.6521</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4866</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6588</v>
+        <v>-0.538</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6686</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3649</v>
+        <v>0.9749</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3649</v>
+        <v>0.9749</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9042</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4226</v>
+        <v>-0.2826</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4817</v>
+        <v>0.2908</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9281</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6658</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2624</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>T. FIELDS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1377</v>
+        <v>-0.9041</v>
       </c>
       <c r="E16" t="n">
-        <v>0.41</v>
+        <v>3.6357</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7277</v>
+        <v>-4.5397</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1546</v>
+        <v>0.4651</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1042</v>
+        <v>0.2495</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0504</v>
+        <v>0.2157</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6926</v>
+        <v>4.4769</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6521</v>
+        <v>3.7399</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>0.737</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.538</v>
+        <v>-4.0118</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-3.4904</v>
       </c>
       <c r="O16" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.5214</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9749</v>
+        <v>0.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9749</v>
+        <v>1.5599</v>
       </c>
       <c r="S16" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.5391</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2826</v>
+        <v>0.3287</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2908</v>
+        <v>-0.8678</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3075</v>
+        <v>-1.0868</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3075</v>
+        <v>-0.4275</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.6592</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3075</v>
+        <v>1.6948</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3075</v>
+        <v>0.6173</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.0775</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3075</v>
+        <v>2.9202</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3075</v>
+        <v>1.9886</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.9315</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.2254</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.3714</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1198</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.9499</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.619</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1035</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.5155</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.2307</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3315</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.8992</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. FIELDS</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9041</v>
+        <v>-1.1072</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6357</v>
+        <v>0.3303</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.5397</v>
+        <v>-1.4375</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4651</v>
+        <v>0.9639</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2495</v>
+        <v>0.4049</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2157</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4769</v>
+        <v>1.4431</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7399</v>
+        <v>1.4351</v>
       </c>
       <c r="L18" t="n">
-        <v>0.737</v>
+        <v>0.008</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.0118</v>
+        <v>-0.4792</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.4904</v>
+        <v>-1.0302</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5214</v>
+        <v>0.551</v>
       </c>
       <c r="P18" t="n">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1699</v>
+        <v>-0.9749</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5599</v>
+        <v>0.585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5391</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3287</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8678</v>
+        <v>-0.8642</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2201</v>
+        <v>-0.732</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.0529</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2201</v>
+        <v>-0.6791</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0868</v>
+        <v>-1.2304</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4275</v>
+        <v>-0.4881</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6592</v>
+        <v>-0.7423</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6948</v>
+        <v>-0.4233</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6173</v>
+        <v>-1.0826</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0775</v>
+        <v>0.6593</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9202</v>
+        <v>0.738</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9886</v>
+        <v>0.082</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9315</v>
+        <v>0.656</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2254</v>
+        <v>-1.1613</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3714</v>
+        <v>-1.1646</v>
       </c>
       <c r="O19" t="n">
-        <v>0.146</v>
+        <v>0.0033</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1699</v>
+        <v>-0.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1198</v>
+        <v>-0.9749</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9499</v>
+        <v>0.585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.619</v>
+        <v>-0.2951</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1035</v>
+        <v>-0.2512</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5155</v>
+        <v>-0.0439</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2307</v>
+        <v>-0.122</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3315</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8992</v>
+        <v>-0.122</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1072</v>
+        <v>-2.41</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3303</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4375</v>
+        <v>-2.338</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9639</v>
+        <v>-0.2444</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4049</v>
+        <v>-0.1116</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5590000000000001</v>
+        <v>-0.1328</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4431</v>
+        <v>0.9841</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4351</v>
+        <v>0.9841</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4792</v>
+        <v>-1.2285</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0302</v>
+        <v>-1.0957</v>
       </c>
       <c r="O20" t="n">
-        <v>0.551</v>
+        <v>-0.1328</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.39</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R20" t="n">
-        <v>0.585</v>
+        <v>0.195</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.1655</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8642</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.732</v>
+        <v>-1.2201</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6791</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>T. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2304</v>
+        <v>-2.6527</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4881</v>
+        <v>-2.7385</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7423</v>
+        <v>0.0858</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4233</v>
+        <v>-2.1991</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0826</v>
+        <v>-0.5758</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6593</v>
+        <v>-1.6234</v>
       </c>
       <c r="J21" t="n">
-        <v>0.738</v>
+        <v>-1.32</v>
       </c>
       <c r="K21" t="n">
-        <v>0.082</v>
+        <v>-0.6395</v>
       </c>
       <c r="L21" t="n">
-        <v>0.656</v>
+        <v>-0.6805</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1613</v>
+        <v>-0.8791</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1646</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0033</v>
+        <v>-0.9428</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.39</v>
+        <v>-0.585</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R21" t="n">
-        <v>0.585</v>
+        <v>0.39</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2951</v>
+        <v>-0.5316</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2512</v>
+        <v>-0.4435</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0439</v>
+        <v>-0.0881</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.122</v>
+        <v>0.6629</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.122</v>
+        <v>0.6629</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.41</v>
+        <v>-3.2273</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-2.7012</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.338</v>
+        <v>-0.5261</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2444</v>
+        <v>-2.6034</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1116</v>
+        <v>-1.3121</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1328</v>
+        <v>-1.2913</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9841</v>
+        <v>-1.5829</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9841</v>
+        <v>-0.2784</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.3045</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2285</v>
+        <v>-1.0205</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0957</v>
+        <v>-1.0337</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1328</v>
+        <v>0.0132</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7799</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9749</v>
+        <v>-2.1448</v>
       </c>
       <c r="R22" t="n">
-        <v>0.195</v>
+        <v>0.9749</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1655</v>
+        <v>-0.605</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.1935</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.4114</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2201</v>
+        <v>1.151</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2201</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. VAN BRANDWIJK</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6527</v>
+        <v>-4.8465</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7385</v>
+        <v>-3.7064</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0858</v>
+        <v>-1.1401</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1991</v>
+        <v>-3.3102</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5758</v>
+        <v>-3.4317</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6234</v>
+        <v>0.1215</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.32</v>
+        <v>-1.6829</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6395</v>
+        <v>-2.193</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6805</v>
+        <v>0.51</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8791</v>
+        <v>-1.6272</v>
       </c>
       <c r="N23" t="n">
-        <v>0.06370000000000001</v>
+        <v>-1.2387</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9428</v>
+        <v>-0.3885</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.585</v>
+        <v>-1.7549</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9749</v>
+        <v>-3.1198</v>
       </c>
       <c r="R23" t="n">
-        <v>0.39</v>
+        <v>1.3649</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5316</v>
+        <v>-0.3386</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4435</v>
+        <v>0.2606</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0881</v>
+        <v>-0.5992</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6629</v>
+        <v>0.5571</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.8357</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6629</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2273</v>
+        <v>-8.4901</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7012</v>
+        <v>-6.055</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5261</v>
+        <v>-2.4351</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6034</v>
+        <v>-5.0952</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3121</v>
+        <v>-3.9852</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2913</v>
+        <v>-1.11</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5829</v>
+        <v>-2.4415</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2784</v>
+        <v>-1.5905</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3045</v>
+        <v>-0.851</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0205</v>
+        <v>-2.6537</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0337</v>
+        <v>-2.3947</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0132</v>
+        <v>-0.259</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1699</v>
+        <v>-2.3398</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1448</v>
+        <v>-3.8997</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9749</v>
+        <v>1.5599</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.605</v>
+        <v>-0.6706</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1935</v>
+        <v>-0.5495</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4114</v>
+        <v>-0.1211</v>
       </c>
       <c r="V24" t="n">
-        <v>1.151</v>
+        <v>-0.3844</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2201</v>
+        <v>0.8357</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,235 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8465</v>
+        <v>-18.8044</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7064</v>
+        <v>-3.998999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1401</v>
+        <v>-14.8051</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3102</v>
+        <v>-10.2593</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.4317</v>
+        <v>-12.9813</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1215</v>
+        <v>2.722</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6829</v>
+        <v>8.111899999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.193</v>
+        <v>4.160500000000003</v>
       </c>
       <c r="L25" t="n">
-        <v>0.51</v>
+        <v>3.9512</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6272</v>
+        <v>-18.3712</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2387</v>
+        <v>-17.142</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3885</v>
+        <v>-1.2291</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.7549</v>
+        <v>-4.8747</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.1198</v>
+        <v>-17.5486</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3649</v>
+        <v>12.6742</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3386</v>
+        <v>-5.168900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2606</v>
+        <v>-1.8438</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5992</v>
+        <v>-3.3253</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5571</v>
+        <v>1.4984</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8357</v>
+        <v>7.281499999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536129_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A. MARIN ORTEGA</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CB ALGECIRAS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-8.4901</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-6.055</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-2.4351</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-5.0952</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-3.9852</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-2.4415</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-1.5905</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-0.851</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-2.6537</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-2.3947</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.259</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-2.3398</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-3.8997</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.5599</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-0.6706</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.5495</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.1211</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-0.3844</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.8357</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536129_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CB ALGECIRAS</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-18.8045</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-3.999</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-14.8051</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-10.2593</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-12.9814</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.722</v>
-      </c>
-      <c r="J27" t="n">
-        <v>8.111899999999999</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.160500000000001</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3.9512</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-18.3712</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-17.142</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-1.2291</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-4.8747</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-17.5486</v>
-      </c>
-      <c r="R27" t="n">
-        <v>12.6742</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-5.168900000000001</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-1.8438</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-3.3253</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.4984</v>
-      </c>
-      <c r="W27" t="n">
-        <v>7.281499999999999</v>
-      </c>
-      <c r="X27" t="n">
         <v>-5.782999999999999</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
